--- a/ig/improve-doc/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
+++ b/ig/improve-doc/ValueSet-JDV-J286-ProfilUtilisateurReferentielNational-ROR.xlsx
@@ -153,7 +153,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R369-ProfilUtilisateurReferentielNational/FHIR/TRE_R369-ProfilUtilisateurReferentielNational</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R369_ProfilUtilisateurReferentielNational/FHIR/TRE-R369-ProfilUtilisateurReferentielNational</t>
   </si>
 </sst>
 </file>
